--- a/data/trans_bre/P57_R-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/P57_R-Habitat-trans_bre.xlsx
@@ -601,22 +601,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,3; 9,87</t>
+          <t>0,65; 9,71</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-0,72; 6,37</t>
+          <t>-0,75; 6,41</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,23; 59,01</t>
+          <t>2,89; 57,46</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-4,11; 44,59</t>
+          <t>-3,75; 44,47</t>
         </is>
       </c>
     </row>
@@ -661,22 +661,22 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,04; 7,76</t>
+          <t>-0,02; 7,54</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>3,68; 12,75</t>
+          <t>3,89; 12,96</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,12; 42,09</t>
+          <t>-0,17; 41,81</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>28,65; 224,14</t>
+          <t>29,96; 247,69</t>
         </is>
       </c>
     </row>
@@ -721,22 +721,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,78; 6,06</t>
+          <t>-2,02; 6,44</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-6,05; 1,92</t>
+          <t>-6,73; 1,8</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-9,42; 39,79</t>
+          <t>-9,92; 42,02</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-59,67; 24,45</t>
+          <t>-62,39; 20,47</t>
         </is>
       </c>
     </row>
@@ -781,22 +781,22 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>4,39; 11,77</t>
+          <t>4,44; 12,0</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-1,03; 6,71</t>
+          <t>-1,2; 6,87</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>23,61; 74,22</t>
+          <t>23,16; 75,59</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-5,81; 44,78</t>
+          <t>-6,4; 47,5</t>
         </is>
       </c>
     </row>
@@ -841,22 +841,22 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>2,96; 6,96</t>
+          <t>2,9; 6,99</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,4; 6,42</t>
+          <t>0,23; 6,25</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>14,74; 39,33</t>
+          <t>15,13; 40,28</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3,75; 63,47</t>
+          <t>3,27; 61,0</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P57_R-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/P57_R-Habitat-trans_bre.xlsx
@@ -578,7 +578,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>2,97</t>
+          <t>3,46</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -588,7 +588,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>18,19%</t>
+          <t>21,82%</t>
         </is>
       </c>
     </row>
@@ -601,22 +601,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,65; 9,71</t>
+          <t>0,28; 9,62</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-0,75; 6,41</t>
+          <t>-0,65; 6,93</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2,89; 57,46</t>
+          <t>1,58; 57,47</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-3,75; 44,47</t>
+          <t>-2,95; 51,6</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>7,46</t>
+          <t>5,25</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -648,7 +648,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>77,35%</t>
+          <t>43,45%</t>
         </is>
       </c>
     </row>
@@ -661,22 +661,22 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-0,02; 7,54</t>
+          <t>-0,21; 7,35</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>3,89; 12,96</t>
+          <t>2,17; 7,81</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-0,17; 41,81</t>
+          <t>-0,94; 39,8</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>29,96; 247,69</t>
+          <t>16,79; 75,59</t>
         </is>
       </c>
     </row>
@@ -698,7 +698,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>-1,46</t>
+          <t>1,2</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -708,7 +708,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-16,43%</t>
+          <t>13,31%</t>
         </is>
       </c>
     </row>
@@ -721,22 +721,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-2,02; 6,44</t>
+          <t>-2,09; 6,4</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-6,73; 1,8</t>
+          <t>-1,88; 4,23</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-9,92; 42,02</t>
+          <t>-10,44; 43,01</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-62,39; 20,47</t>
+          <t>-17,03; 61,61</t>
         </is>
       </c>
     </row>
@@ -758,7 +758,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>3,34</t>
+          <t>4,41</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -768,7 +768,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>20,65%</t>
+          <t>26,49%</t>
         </is>
       </c>
     </row>
@@ -781,22 +781,22 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>4,44; 12,0</t>
+          <t>4,18; 12,03</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-1,2; 6,87</t>
+          <t>1,21; 7,55</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>23,16; 75,59</t>
+          <t>21,12; 77,31</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-6,4; 47,5</t>
+          <t>6,81; 51,18</t>
         </is>
       </c>
     </row>
@@ -818,7 +818,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>3,3</t>
+          <t>3,89</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -828,7 +828,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>26,5%</t>
+          <t>29,07%</t>
         </is>
       </c>
     </row>
@@ -841,22 +841,22 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>2,9; 6,99</t>
+          <t>2,83; 6,94</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,23; 6,25</t>
+          <t>2,31; 5,37</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>15,13; 40,28</t>
+          <t>14,91; 40,03</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3,27; 61,0</t>
+          <t>15,92; 41,97</t>
         </is>
       </c>
     </row>
